--- a/Arabic Sarf Template.xlsx
+++ b/Arabic Sarf Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\HGWC\Aalim Course\Books and Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C450FC-F298-40AB-BD27-46092A667092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57CA920-12D2-40C1-979B-45851CF7E645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="12900" xr2:uid="{0CB986DA-EAA0-487E-8422-15F5F0704A7F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{0CB986DA-EAA0-487E-8422-15F5F0704A7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Base - Template" sheetId="1" r:id="rId1"/>
@@ -2967,8 +2967,8 @@
   <dimension ref="A1:U78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="9.140625" customWidth="1"/>
     <col min="11" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -2977,7 +2977,7 @@
     <col min="22" max="22" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
         <v>0</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D2" t="s">
         <v>10</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D3" t="str">
         <f>VLOOKUP(C8,Q1:R7,2,FALSE)</f>
         <v>َ</v>
@@ -3647,8 +3647,8 @@
         <v>تَكْرُمُوْنَ</v>
       </c>
       <c r="F15" t="str">
-        <f>C5&amp;F1&amp;C6&amp;E1&amp;C7&amp;G1&amp;F2&amp;F1&amp;H2&amp;D1&amp;D2</f>
-        <v>كُرِمْتُمَا</v>
+        <f>C5&amp;F1&amp;C6&amp;E1&amp;C7&amp;G1&amp;F2&amp;F1&amp;H2&amp;G1</f>
+        <v>كُرِمْتُمْ</v>
       </c>
       <c r="G15" t="str">
         <f>F2&amp;F1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;F1&amp;E2&amp;G1&amp;G2&amp;D1</f>

--- a/Arabic Sarf Template.xlsx
+++ b/Arabic Sarf Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\HGWC\Aalim Course\Books and Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57CA920-12D2-40C1-979B-45851CF7E645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95094AF-FCCB-41C0-84B7-3BE0E14F88E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{0CB986DA-EAA0-487E-8422-15F5F0704A7F}"/>
   </bookViews>
@@ -316,163 +316,163 @@
     <t>سَمِعَ-يَسْمَعُ</t>
   </si>
   <si>
+    <t>كَرُمَ-يَكْرُمُ</t>
+  </si>
+  <si>
+    <t>حَسِبَ-يَحْسِبُ</t>
+  </si>
+  <si>
+    <t>Maazi</t>
+  </si>
+  <si>
+    <t>Muzare</t>
+  </si>
+  <si>
+    <t>Amr</t>
+  </si>
+  <si>
+    <t>Zarf Zaman</t>
+  </si>
+  <si>
+    <t>اسم الفاعل</t>
+  </si>
+  <si>
+    <t>اسم المفعول</t>
+  </si>
+  <si>
+    <t>اسم التفضيل</t>
+  </si>
+  <si>
+    <t>اسم الظرف</t>
+  </si>
+  <si>
+    <t>صفة مشبة</t>
+  </si>
+  <si>
+    <t>فَعْلَانُ</t>
+  </si>
+  <si>
+    <t>أَفْعَلُ</t>
+  </si>
+  <si>
+    <t>فَعُوْلٌ</t>
+  </si>
+  <si>
+    <t>فُعَالٌ</t>
+  </si>
+  <si>
+    <t>فَعِيْلٌ</t>
+  </si>
+  <si>
+    <t>اسم مبالغة</t>
+  </si>
+  <si>
+    <t>فُعُّوْلٌ</t>
+  </si>
+  <si>
+    <t>فَعُّوْلٌ</t>
+  </si>
+  <si>
+    <t>فَاعُوْلٌ</t>
+  </si>
+  <si>
+    <t>فُعَّالٌ</t>
+  </si>
+  <si>
+    <t>فَعَّالٌ</t>
+  </si>
+  <si>
+    <t>اسم الآلة</t>
+  </si>
+  <si>
+    <t>مِفْعَالٌ</t>
+  </si>
+  <si>
+    <t>مِفْعَلَةٌ</t>
+  </si>
+  <si>
+    <t>مِفْعَلٌ</t>
+  </si>
+  <si>
+    <t>مِفْعَالَانِ</t>
+  </si>
+  <si>
+    <t>مِفْعَلَتَانِ</t>
+  </si>
+  <si>
+    <t>مِفْعَلَانِ</t>
+  </si>
+  <si>
+    <t>مَفَاعِيْلُ</t>
+  </si>
+  <si>
+    <t>مَفَاعِلُ</t>
+  </si>
+  <si>
+    <t>ثلاثى مزيد فيه - صرف صغير</t>
+  </si>
+  <si>
+    <t>إكراما</t>
+  </si>
+  <si>
+    <t>افعال</t>
+  </si>
+  <si>
+    <t>تصريفا</t>
+  </si>
+  <si>
+    <t>تفعيل</t>
+  </si>
+  <si>
+    <t>مقاتلة</t>
+  </si>
+  <si>
+    <t>مفاعلة</t>
+  </si>
+  <si>
+    <t>تفهّما</t>
+  </si>
+  <si>
+    <t>تفعُّل</t>
+  </si>
+  <si>
+    <t>تغافلا</t>
+  </si>
+  <si>
+    <t>تفاعل</t>
+  </si>
+  <si>
+    <t>انكسارا</t>
+  </si>
+  <si>
+    <t>انفعال</t>
+  </si>
+  <si>
+    <t>اجتنابا</t>
+  </si>
+  <si>
+    <t>افتعال</t>
+  </si>
+  <si>
+    <t>احمرارا</t>
+  </si>
+  <si>
+    <t>افعلال</t>
+  </si>
+  <si>
+    <t>استغفارا</t>
+  </si>
+  <si>
+    <t>استفعال</t>
+  </si>
+  <si>
+    <t>Ism Zarf</t>
+  </si>
+  <si>
     <t>ر</t>
   </si>
   <si>
-    <t>كَرُمَ-يَكْرُمُ</t>
-  </si>
-  <si>
-    <t>حَسِبَ-يَحْسِبُ</t>
-  </si>
-  <si>
-    <t>Maazi</t>
-  </si>
-  <si>
-    <t>Muzare</t>
-  </si>
-  <si>
-    <t>Amr</t>
-  </si>
-  <si>
-    <t>Zarf Zaman</t>
-  </si>
-  <si>
-    <t>اسم الفاعل</t>
-  </si>
-  <si>
-    <t>اسم المفعول</t>
-  </si>
-  <si>
-    <t>اسم التفضيل</t>
-  </si>
-  <si>
-    <t>اسم الظرف</t>
-  </si>
-  <si>
-    <t>صفة مشبة</t>
-  </si>
-  <si>
-    <t>فَعْلَانُ</t>
-  </si>
-  <si>
-    <t>أَفْعَلُ</t>
-  </si>
-  <si>
-    <t>فَعُوْلٌ</t>
-  </si>
-  <si>
-    <t>فُعَالٌ</t>
-  </si>
-  <si>
-    <t>فَعِيْلٌ</t>
-  </si>
-  <si>
-    <t>اسم مبالغة</t>
-  </si>
-  <si>
-    <t>فُعُّوْلٌ</t>
-  </si>
-  <si>
-    <t>فَعُّوْلٌ</t>
-  </si>
-  <si>
-    <t>فَاعُوْلٌ</t>
-  </si>
-  <si>
-    <t>فُعَّالٌ</t>
-  </si>
-  <si>
-    <t>فَعَّالٌ</t>
-  </si>
-  <si>
-    <t>اسم الآلة</t>
-  </si>
-  <si>
-    <t>مِفْعَالٌ</t>
-  </si>
-  <si>
-    <t>مِفْعَلَةٌ</t>
-  </si>
-  <si>
-    <t>مِفْعَلٌ</t>
-  </si>
-  <si>
-    <t>مِفْعَالَانِ</t>
-  </si>
-  <si>
-    <t>مِفْعَلَتَانِ</t>
-  </si>
-  <si>
-    <t>مِفْعَلَانِ</t>
-  </si>
-  <si>
-    <t>مَفَاعِيْلُ</t>
-  </si>
-  <si>
-    <t>مَفَاعِلُ</t>
-  </si>
-  <si>
-    <t>ثلاثى مزيد فيه - صرف صغير</t>
-  </si>
-  <si>
-    <t>إكراما</t>
-  </si>
-  <si>
-    <t>افعال</t>
-  </si>
-  <si>
-    <t>تصريفا</t>
-  </si>
-  <si>
-    <t>تفعيل</t>
-  </si>
-  <si>
-    <t>مقاتلة</t>
-  </si>
-  <si>
-    <t>مفاعلة</t>
-  </si>
-  <si>
-    <t>تفهّما</t>
-  </si>
-  <si>
-    <t>تفعُّل</t>
-  </si>
-  <si>
-    <t>تغافلا</t>
-  </si>
-  <si>
-    <t>تفاعل</t>
-  </si>
-  <si>
-    <t>انكسارا</t>
-  </si>
-  <si>
-    <t>انفعال</t>
-  </si>
-  <si>
-    <t>اجتنابا</t>
-  </si>
-  <si>
-    <t>افتعال</t>
-  </si>
-  <si>
-    <t>احمرارا</t>
-  </si>
-  <si>
-    <t>افعلال</t>
-  </si>
-  <si>
-    <t>استغفارا</t>
-  </si>
-  <si>
-    <t>استفعال</t>
-  </si>
-  <si>
     <t>ك</t>
-  </si>
-  <si>
-    <t>Ism Zarf</t>
   </si>
 </sst>
 </file>
@@ -542,7 +542,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -569,6 +569,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -696,7 +699,7 @@
           <xdr:rowOff>171450</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>21</xdr:col>
+          <xdr:col>16</xdr:col>
           <xdr:colOff>200025</xdr:colOff>
           <xdr:row>61</xdr:row>
           <xdr:rowOff>9525</xdr:rowOff>
@@ -782,7 +785,7 @@
           <xdr:rowOff>171450</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>21</xdr:col>
+          <xdr:col>16</xdr:col>
           <xdr:colOff>200025</xdr:colOff>
           <xdr:row>62</xdr:row>
           <xdr:rowOff>9525</xdr:rowOff>
@@ -868,7 +871,7 @@
           <xdr:rowOff>171450</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>21</xdr:col>
+          <xdr:col>16</xdr:col>
           <xdr:colOff>200025</xdr:colOff>
           <xdr:row>63</xdr:row>
           <xdr:rowOff>9525</xdr:rowOff>
@@ -954,7 +957,7 @@
           <xdr:rowOff>171450</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>21</xdr:col>
+          <xdr:col>16</xdr:col>
           <xdr:colOff>200025</xdr:colOff>
           <xdr:row>64</xdr:row>
           <xdr:rowOff>9525</xdr:rowOff>
@@ -1040,7 +1043,7 @@
           <xdr:rowOff>171450</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>21</xdr:col>
+          <xdr:col>16</xdr:col>
           <xdr:colOff>200025</xdr:colOff>
           <xdr:row>65</xdr:row>
           <xdr:rowOff>9525</xdr:rowOff>
@@ -1126,7 +1129,7 @@
           <xdr:rowOff>171450</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>21</xdr:col>
+          <xdr:col>16</xdr:col>
           <xdr:colOff>200025</xdr:colOff>
           <xdr:row>67</xdr:row>
           <xdr:rowOff>9525</xdr:rowOff>
@@ -1212,7 +1215,7 @@
           <xdr:rowOff>171450</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>21</xdr:col>
+          <xdr:col>16</xdr:col>
           <xdr:colOff>200025</xdr:colOff>
           <xdr:row>68</xdr:row>
           <xdr:rowOff>9525</xdr:rowOff>
@@ -1298,7 +1301,7 @@
           <xdr:rowOff>171450</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>21</xdr:col>
+          <xdr:col>16</xdr:col>
           <xdr:colOff>200025</xdr:colOff>
           <xdr:row>69</xdr:row>
           <xdr:rowOff>9525</xdr:rowOff>
@@ -1384,7 +1387,7 @@
           <xdr:rowOff>171450</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>21</xdr:col>
+          <xdr:col>16</xdr:col>
           <xdr:colOff>200025</xdr:colOff>
           <xdr:row>70</xdr:row>
           <xdr:rowOff>9525</xdr:rowOff>
@@ -2972,8 +2975,12 @@
     <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="9.140625" customWidth="1"/>
     <col min="11" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="0" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="13" max="14" width="9.140625" customWidth="1"/>
+    <col min="17" max="17" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.140625" customWidth="1"/>
     <col min="22" max="22" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3134,10 +3141,10 @@
       <c r="L4" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="N4" s="12" t="s">
+      <c r="N4" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3151,7 +3158,7 @@
         <v>يَكْرُم</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D5" t="str">
         <f>C5&amp;D1&amp;C6&amp;D3&amp;C7&amp;D1</f>
@@ -3223,7 +3230,7 @@
         <v>يَكْرُمَا</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="D6" t="str">
         <f>C5&amp;D1&amp;C6&amp;D3&amp;C7&amp;D1&amp;D2</f>
@@ -3262,7 +3269,7 @@
         <v>لِيَكْرُمَانِّ</v>
       </c>
       <c r="Q6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R6" t="s">
         <v>2</v>
@@ -3334,7 +3341,7 @@
         <v>لِيَكْرُمُنْ</v>
       </c>
       <c r="Q7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R7" t="s">
         <v>1</v>
@@ -3410,16 +3417,16 @@
         <v>لِتَكْرُمَنْ</v>
       </c>
       <c r="R9" t="s">
+        <v>39</v>
+      </c>
+      <c r="S9" t="s">
         <v>40</v>
       </c>
-      <c r="S9" t="s">
+      <c r="T9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T9" s="2" t="s">
+      <c r="U9" t="s">
         <v>42</v>
-      </c>
-      <c r="U9" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -3524,7 +3531,7 @@
       <c r="M12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -3573,12 +3580,12 @@
         <v>اُكْرُمْ</v>
       </c>
       <c r="M13" s="2" t="str">
-        <f>D2&amp;E1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;G2&amp;H1&amp;D1</f>
-        <v>اِكْرُمَنَّ</v>
+        <f>D2&amp;L3&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;G2&amp;H1&amp;D1</f>
+        <v>اُكْرُمَنَّ</v>
       </c>
       <c r="N13" t="str">
-        <f>D2&amp;E1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;G2&amp;G1</f>
-        <v>اِكْرُمَنْ</v>
+        <f>D2&amp;L3&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;G2&amp;G1</f>
+        <v>اُكْرُمَنْ</v>
       </c>
       <c r="T13" s="2"/>
     </row>
@@ -3624,8 +3631,8 @@
         <v>اُكْرُمَا</v>
       </c>
       <c r="M14" s="2" t="str">
-        <f>D2&amp;E1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;D2&amp;G2&amp;H1&amp;E1</f>
-        <v>اِكْرُمَانِّ</v>
+        <f>D2&amp;L3&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;D2&amp;G2&amp;H1&amp;E1</f>
+        <v>اُكْرُمَانِّ</v>
       </c>
       <c r="T14" s="2"/>
     </row>
@@ -3675,12 +3682,12 @@
         <v>اُكْرُمُوْا</v>
       </c>
       <c r="M15" s="2" t="str">
-        <f>D2&amp;E1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;F1&amp;G2&amp;H1&amp;D1</f>
-        <v>اِكْرُمُنَّ</v>
+        <f>D2&amp;L3&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;F1&amp;G2&amp;H1&amp;D1</f>
+        <v>اُكْرُمُنَّ</v>
       </c>
       <c r="N15" t="str">
-        <f>D2&amp;E1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;F1&amp;G2&amp;G1</f>
-        <v>اِكْرُمُنْ</v>
+        <f>D2&amp;L3&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;F1&amp;G2&amp;G1</f>
+        <v>اُكْرُمُنْ</v>
       </c>
       <c r="T15" s="2"/>
     </row>
@@ -3734,12 +3741,12 @@
         <v>اُكْرُمِيْ</v>
       </c>
       <c r="M17" s="2" t="str">
-        <f>D2&amp;E1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;E1&amp;G2&amp;H1&amp;D1</f>
-        <v>اِكْرُمِنَّ</v>
+        <f>D2&amp;L3&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;E1&amp;G2&amp;H1&amp;D1</f>
+        <v>اُكْرُمِنَّ</v>
       </c>
       <c r="N17" t="str">
-        <f>D2&amp;E1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;E1&amp;G2&amp;G1</f>
-        <v>اِكْرُمِنْ</v>
+        <f>D2&amp;L3&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;E1&amp;G2&amp;G1</f>
+        <v>اُكْرُمِنْ</v>
       </c>
       <c r="T17" s="2"/>
     </row>
@@ -3781,12 +3788,12 @@
         <v>لَتَكْرُمَانِّ</v>
       </c>
       <c r="L18" s="10" t="str">
-        <f>D2&amp;L3&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;E3&amp;D2</f>
-        <v>اُكْرُمُا</v>
+        <f>D2&amp;L3&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;D2</f>
+        <v>اُكْرُمَا</v>
       </c>
       <c r="M18" s="11" t="str">
-        <f>D2&amp;E1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;D2&amp;G2&amp;H1&amp;E1</f>
-        <v>اِكْرُمَانِّ</v>
+        <f>D2&amp;L3&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;D2&amp;G2&amp;H1&amp;E1</f>
+        <v>اُكْرُمَانِّ</v>
       </c>
       <c r="T18" s="11"/>
     </row>
@@ -3832,8 +3839,8 @@
         <v>اُكْرُمْنَ</v>
       </c>
       <c r="M19" s="2" t="str">
-        <f>D2&amp;E1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;G1&amp;G2&amp;D1&amp;D2&amp;G2&amp;H1&amp;E1</f>
-        <v>اِكْرُمْنَانِّ</v>
+        <f>D2&amp;L3&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;G1&amp;G2&amp;D1&amp;D2&amp;G2&amp;H1&amp;E1</f>
+        <v>اُكْرُمْنَانِّ</v>
       </c>
       <c r="T19" s="2"/>
     </row>
@@ -3956,14 +3963,14 @@
       <c r="T23" s="2"/>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D24" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
+      <c r="D24" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D25" t="str">
@@ -4010,14 +4017,14 @@
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D28" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
+      <c r="D28" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D29" t="str">
@@ -4064,14 +4071,14 @@
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D32" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
+      <c r="D32" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
     </row>
     <row r="33" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D33" t="str">
@@ -4110,14 +4117,14 @@
       </c>
     </row>
     <row r="36" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D36" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
+      <c r="D36" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
     </row>
     <row r="37" spans="4:9" x14ac:dyDescent="0.25">
       <c r="G37" t="str">
@@ -4144,14 +4151,14 @@
       </c>
     </row>
     <row r="40" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D40" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
+      <c r="D40" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
     </row>
     <row r="41" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D41" s="8"/>
@@ -4182,19 +4189,19 @@
     <row r="43" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D43" s="3"/>
       <c r="E43" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="H43" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="I43" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="44" spans="4:9" x14ac:dyDescent="0.25">
@@ -4229,14 +4236,14 @@
       <c r="I45" s="3"/>
     </row>
     <row r="46" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D46" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
+      <c r="D46" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
     </row>
     <row r="47" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D47" s="8"/>
@@ -4268,22 +4275,22 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D49" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E49" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="F49" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="G49" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H49" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G49" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H49" s="4" t="s">
+      <c r="I49" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -4321,14 +4328,14 @@
       <c r="I51" s="3"/>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D52" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
+      <c r="D52" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D53" s="8"/>
@@ -4358,21 +4365,21 @@
         <v/>
       </c>
       <c r="E55" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F55" s="5" t="str">
         <f>IF(G54, H2&amp;E1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;D1&amp;K2&amp;K1,"")</f>
         <v/>
       </c>
       <c r="G55" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H55" s="5" t="str">
         <f>IF(I54, H2&amp;E1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;K1,"")</f>
         <v/>
       </c>
       <c r="I55" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -4381,21 +4388,21 @@
         <v/>
       </c>
       <c r="E56" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F56" s="5" t="str">
         <f>IF(G54, H2&amp;E1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;D1&amp;F2&amp;D1&amp;D2&amp;G2&amp;E1,"")</f>
         <v/>
       </c>
       <c r="G56" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H56" s="5" t="str">
         <f>IF(I54, H2&amp;E1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;D1&amp;D2&amp;G2&amp;E1,"")</f>
         <v/>
       </c>
       <c r="I56" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -4404,39 +4411,39 @@
         <v/>
       </c>
       <c r="E57" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F57" s="5" t="str">
         <f>IF(G54, H2&amp;D1&amp;C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;F1,"")</f>
         <v/>
       </c>
       <c r="G57" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H57" s="5" t="str">
         <f>IF(I54, H2&amp;D1&amp;C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;F1,"")</f>
         <v/>
       </c>
       <c r="I57" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D59" s="14" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="59" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D59" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
-      <c r="K59" s="13"/>
-      <c r="L59" s="13"/>
-      <c r="M59" s="13"/>
-      <c r="N59" s="13"/>
-      <c r="O59" s="13"/>
-      <c r="P59" s="13"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
+      <c r="L59" s="14"/>
+      <c r="M59" s="14"/>
+      <c r="N59" s="14"/>
+      <c r="O59" s="14"/>
+      <c r="P59" s="14"/>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
@@ -4496,10 +4503,10 @@
         <v/>
       </c>
       <c r="N61" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="O61" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="O61" s="7" t="s">
-        <v>71</v>
       </c>
       <c r="Q61" t="b">
         <v>0</v>
@@ -4548,10 +4555,10 @@
         <v/>
       </c>
       <c r="N62" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="O62" s="7" t="s">
         <v>72</v>
-      </c>
-      <c r="O62" s="7" t="s">
-        <v>73</v>
       </c>
       <c r="Q62" t="b">
         <v>0</v>
@@ -4600,10 +4607,10 @@
         <v/>
       </c>
       <c r="N63" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="O63" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="O63" s="7" t="s">
-        <v>75</v>
       </c>
       <c r="Q63" t="b">
         <v>0</v>
@@ -4652,10 +4659,10 @@
         <v/>
       </c>
       <c r="N64" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="O64" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="O64" s="7" t="s">
-        <v>77</v>
       </c>
       <c r="Q64" t="b">
         <v>0</v>
@@ -4704,10 +4711,10 @@
         <v/>
       </c>
       <c r="N65" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O65" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="O65" s="7" t="s">
-        <v>79</v>
       </c>
       <c r="Q65" t="b">
         <v>0</v>
@@ -4761,10 +4768,10 @@
         <v/>
       </c>
       <c r="N67" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O67" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="O67" s="7" t="s">
-        <v>81</v>
       </c>
       <c r="Q67" t="b">
         <v>0</v>
@@ -4797,10 +4804,10 @@
         <v/>
       </c>
       <c r="N68" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="O68" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="O68" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="Q68" t="b">
         <v>0</v>
@@ -4833,10 +4840,10 @@
         <v/>
       </c>
       <c r="N69" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="O69" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="O69" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="Q69" t="b">
         <v>0</v>
@@ -4885,10 +4892,10 @@
         <v/>
       </c>
       <c r="N70" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="O70" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="O70" s="7" t="s">
-        <v>87</v>
       </c>
       <c r="Q70" t="b">
         <v>0</v>
@@ -4958,7 +4965,7 @@
                     <xdr:rowOff>171450</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>21</xdr:col>
+                    <xdr:col>16</xdr:col>
                     <xdr:colOff>200025</xdr:colOff>
                     <xdr:row>61</xdr:row>
                     <xdr:rowOff>9525</xdr:rowOff>
@@ -4980,7 +4987,7 @@
                     <xdr:rowOff>171450</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>21</xdr:col>
+                    <xdr:col>16</xdr:col>
                     <xdr:colOff>200025</xdr:colOff>
                     <xdr:row>62</xdr:row>
                     <xdr:rowOff>9525</xdr:rowOff>
@@ -5002,7 +5009,7 @@
                     <xdr:rowOff>171450</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>21</xdr:col>
+                    <xdr:col>16</xdr:col>
                     <xdr:colOff>200025</xdr:colOff>
                     <xdr:row>63</xdr:row>
                     <xdr:rowOff>9525</xdr:rowOff>
@@ -5024,7 +5031,7 @@
                     <xdr:rowOff>171450</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>21</xdr:col>
+                    <xdr:col>16</xdr:col>
                     <xdr:colOff>200025</xdr:colOff>
                     <xdr:row>64</xdr:row>
                     <xdr:rowOff>9525</xdr:rowOff>
@@ -5046,7 +5053,7 @@
                     <xdr:rowOff>171450</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>21</xdr:col>
+                    <xdr:col>16</xdr:col>
                     <xdr:colOff>200025</xdr:colOff>
                     <xdr:row>65</xdr:row>
                     <xdr:rowOff>9525</xdr:rowOff>
@@ -5068,7 +5075,7 @@
                     <xdr:rowOff>171450</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>21</xdr:col>
+                    <xdr:col>16</xdr:col>
                     <xdr:colOff>200025</xdr:colOff>
                     <xdr:row>67</xdr:row>
                     <xdr:rowOff>9525</xdr:rowOff>
@@ -5090,7 +5097,7 @@
                     <xdr:rowOff>171450</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>21</xdr:col>
+                    <xdr:col>16</xdr:col>
                     <xdr:colOff>200025</xdr:colOff>
                     <xdr:row>68</xdr:row>
                     <xdr:rowOff>9525</xdr:rowOff>
@@ -5112,7 +5119,7 @@
                     <xdr:rowOff>171450</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>21</xdr:col>
+                    <xdr:col>16</xdr:col>
                     <xdr:colOff>200025</xdr:colOff>
                     <xdr:row>69</xdr:row>
                     <xdr:rowOff>9525</xdr:rowOff>
@@ -5134,7 +5141,7 @@
                     <xdr:rowOff>171450</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>21</xdr:col>
+                    <xdr:col>16</xdr:col>
                     <xdr:colOff>200025</xdr:colOff>
                     <xdr:row>70</xdr:row>
                     <xdr:rowOff>9525</xdr:rowOff>

--- a/Arabic Sarf Template.xlsx
+++ b/Arabic Sarf Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\HGWC\Aalim Course\Books and Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95094AF-FCCB-41C0-84B7-3BE0E14F88E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB1A0D1-EF4C-4D02-8E86-A0838AB042B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{0CB986DA-EAA0-487E-8422-15F5F0704A7F}"/>
+    <workbookView xWindow="8190" yWindow="0" windowWidth="15810" windowHeight="12900" xr2:uid="{0CB986DA-EAA0-487E-8422-15F5F0704A7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Base - Template" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,8 @@
             <family val="2"/>
           </rPr>
           <t>أَفْعَلُ
- pattern for both gender and number. If used as an attribute then other pattern applicable.</t>
+ pattern for both gender and number. If used as an attribute then other pattern applicable.
+The Plural has two options</t>
         </r>
       </text>
     </comment>
@@ -203,7 +204,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
   <si>
     <t>َ</t>
   </si>
@@ -274,24 +275,9 @@
     <t xml:space="preserve">لَمْ </t>
   </si>
   <si>
-    <t xml:space="preserve">أَنْ </t>
-  </si>
-  <si>
     <t>نَصَرَ-يَنْصُرُ</t>
   </si>
   <si>
-    <t>فعل الماضي مرفوع</t>
-  </si>
-  <si>
-    <t>فعل المضارع مرفوع</t>
-  </si>
-  <si>
-    <t>فعل الماضي مجهول</t>
-  </si>
-  <si>
-    <t>فعل المضارع مجهول</t>
-  </si>
-  <si>
     <t>مجزوم المضرع</t>
   </si>
   <si>
@@ -473,6 +459,27 @@
   </si>
   <si>
     <t>ك</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لَنْ </t>
+  </si>
+  <si>
+    <t>Rafa'</t>
+  </si>
+  <si>
+    <t>Nasab &amp; Jarr</t>
+  </si>
+  <si>
+    <t>الفعل الماضي المرفوع</t>
+  </si>
+  <si>
+    <t>الفعل المضارع المرفوع</t>
+  </si>
+  <si>
+    <t>الفعل الماضي المجهول</t>
+  </si>
+  <si>
+    <t>الفعل المضارع المجهول</t>
   </si>
 </sst>
 </file>
@@ -3081,7 +3088,7 @@
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D3" t="str">
         <f>VLOOKUP(C8,Q1:R7,2,FALSE)</f>
-        <v>َ</v>
+        <v>ُ</v>
       </c>
       <c r="E3" t="str">
         <f>VLOOKUP(C8,Q1:S7,3,FALSE)</f>
@@ -3091,14 +3098,14 @@
         <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="L3" t="str">
         <f>VLOOKUP(C8,Q1:T7,4,FALSE)</f>
         <v>ُ</v>
       </c>
       <c r="Q3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R3" t="s">
         <v>0</v>
@@ -3115,37 +3122,37 @@
     </row>
     <row r="4" spans="1:21" s="1" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="D4" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="J4" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="K4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="L4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="M4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="N4" s="13" t="s">
         <v>30</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="13" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -3158,11 +3165,11 @@
         <v>يَكْرُم</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D5" t="str">
         <f>C5&amp;D1&amp;C6&amp;D3&amp;C7&amp;D1</f>
-        <v>كَرَمَ</v>
+        <v>كَرُمَ</v>
       </c>
       <c r="E5" t="str">
         <f>B5&amp;F1</f>
@@ -3182,7 +3189,7 @@
       </c>
       <c r="I5" t="str">
         <f>I3&amp;B5&amp;D1</f>
-        <v>أَنْ يَكْرُمَ</v>
+        <v>لَنْ يَكْرُمَ</v>
       </c>
       <c r="J5" t="str">
         <f>L2&amp;D1&amp;I2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;G2&amp;H1&amp;D1</f>
@@ -3205,7 +3212,7 @@
         <v>لِيَكْرُمَنْ</v>
       </c>
       <c r="Q5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="R5" t="s">
         <v>1</v>
@@ -3230,11 +3237,11 @@
         <v>يَكْرُمَا</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D6" t="str">
         <f>C5&amp;D1&amp;C6&amp;D3&amp;C7&amp;D1&amp;D2</f>
-        <v>كَرَمَا</v>
+        <v>كَرُمَا</v>
       </c>
       <c r="E6" t="str">
         <f>B6&amp;G2&amp;E1</f>
@@ -3254,7 +3261,7 @@
       </c>
       <c r="I6" t="str">
         <f>I3&amp;B6</f>
-        <v>أَنْ يَكْرُمَا</v>
+        <v>لَنْ يَكْرُمَا</v>
       </c>
       <c r="J6" t="str">
         <f>L2&amp;D1&amp;I2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;D2&amp;G2&amp;H1&amp;E1</f>
@@ -3269,7 +3276,7 @@
         <v>لِيَكْرُمَانِّ</v>
       </c>
       <c r="Q6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="R6" t="s">
         <v>2</v>
@@ -3298,7 +3305,7 @@
       </c>
       <c r="D7" t="str">
         <f>C5&amp;D1&amp;C6&amp;D3&amp;C7&amp;F1&amp;E2&amp;G1&amp;D2</f>
-        <v>كَرَمُوْا</v>
+        <v>كَرُمُوْا</v>
       </c>
       <c r="E7" t="str">
         <f>B7&amp;G2&amp;D1</f>
@@ -3318,7 +3325,7 @@
       </c>
       <c r="I7" t="str">
         <f>I3&amp;B7&amp;D2</f>
-        <v>أَنْ يَكْرُمُوْا</v>
+        <v>لَنْ يَكْرُمُوْا</v>
       </c>
       <c r="J7" t="str">
         <f>L2&amp;D1&amp;I2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;F1&amp;G2&amp;H1&amp;D1</f>
@@ -3341,7 +3348,7 @@
         <v>لِيَكْرُمُنْ</v>
       </c>
       <c r="Q7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R7" t="s">
         <v>1</v>
@@ -3358,7 +3365,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="M8" s="2"/>
       <c r="T8" s="2"/>
@@ -3374,7 +3381,7 @@
       </c>
       <c r="D9" t="str">
         <f>C5&amp;D1&amp;C6&amp;D3&amp;C7&amp;D1&amp;F2&amp;G1</f>
-        <v>كَرَمَتْ</v>
+        <v>كَرُمَتْ</v>
       </c>
       <c r="E9" t="str">
         <f>B9&amp;F1</f>
@@ -3394,7 +3401,7 @@
       </c>
       <c r="I9" t="str">
         <f>I3&amp;B9&amp;D1</f>
-        <v>أَنْ تَكْرُمَ</v>
+        <v>لَنْ تَكْرُمَ</v>
       </c>
       <c r="J9" t="str">
         <f>L2&amp;D1&amp;F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;G2&amp;H1&amp;D1</f>
@@ -3417,16 +3424,16 @@
         <v>لِتَكْرُمَنْ</v>
       </c>
       <c r="R9" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="S9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="U9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -3440,7 +3447,7 @@
       </c>
       <c r="D10" t="str">
         <f>C5&amp;D1&amp;C6&amp;D3&amp;C7&amp;D1&amp;F2&amp;D1&amp;D2</f>
-        <v>كَرَمَتَا</v>
+        <v>كَرُمَتَا</v>
       </c>
       <c r="E10" t="str">
         <f>B10&amp;G2&amp;E1</f>
@@ -3460,7 +3467,7 @@
       </c>
       <c r="I10" t="str">
         <f>I3&amp;B10</f>
-        <v>أَنْ تَكْرُمَا</v>
+        <v>لَنْ تَكْرُمَا</v>
       </c>
       <c r="J10" t="str">
         <f>L2&amp;D1&amp;F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;D2&amp;G2&amp;H1&amp;E1</f>
@@ -3487,7 +3494,7 @@
       </c>
       <c r="D11" t="str">
         <f>C5&amp;D1&amp;C6&amp;D3&amp;C7&amp;G1&amp;G2&amp;D1</f>
-        <v>كَرَمْنَ</v>
+        <v>كَرُمْنَ</v>
       </c>
       <c r="E11" t="str">
         <f>B11</f>
@@ -3507,7 +3514,7 @@
       </c>
       <c r="I11" t="str">
         <f>I3&amp;B11</f>
-        <v>أَنْ يَكْرُمْنَ</v>
+        <v>لَنْ يَكْرُمْنَ</v>
       </c>
       <c r="J11" t="str">
         <f>L2&amp;D1&amp;I2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;G1&amp;G2&amp;D1&amp;D2&amp;G2&amp;H1&amp;E1</f>
@@ -3531,7 +3538,7 @@
       <c r="M12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -3545,7 +3552,7 @@
       </c>
       <c r="D13" t="str">
         <f>C5&amp;D1&amp;C6&amp;D3&amp;C7&amp;G1&amp;F2&amp;D1</f>
-        <v>كَرَمْتَ</v>
+        <v>كَرُمْتَ</v>
       </c>
       <c r="E13" t="str">
         <f>B13&amp;F1</f>
@@ -3565,7 +3572,7 @@
       </c>
       <c r="I13" t="str">
         <f>I3&amp;B13&amp;D1</f>
-        <v>أَنْ تَكْرُمَ</v>
+        <v>لَنْ تَكْرُمَ</v>
       </c>
       <c r="J13" t="str">
         <f>L2&amp;D1&amp;F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;G2&amp;H1&amp;D1</f>
@@ -3600,7 +3607,7 @@
       </c>
       <c r="D14" t="str">
         <f>C5&amp;D1&amp;C6&amp;D3&amp;C7&amp;G1&amp;F2&amp;F1&amp;H2&amp;D1&amp;D2</f>
-        <v>كَرَمْتُمَا</v>
+        <v>كَرُمْتُمَا</v>
       </c>
       <c r="E14" t="str">
         <f>B14&amp;G2&amp;E1</f>
@@ -3620,7 +3627,7 @@
       </c>
       <c r="I14" t="str">
         <f>I3&amp;B14</f>
-        <v>أَنْ تَكْرُمَا</v>
+        <v>لَنْ تَكْرُمَا</v>
       </c>
       <c r="J14" t="str">
         <f>L2&amp;D1&amp;F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;D2&amp;G2&amp;H1&amp;E1</f>
@@ -3647,7 +3654,7 @@
       </c>
       <c r="D15" t="str">
         <f>C5&amp;D1&amp;C6&amp;D3&amp;C7&amp;G1&amp;F2&amp;F1&amp;H2&amp;G1</f>
-        <v>كَرَمْتُمْ</v>
+        <v>كَرُمْتُمْ</v>
       </c>
       <c r="E15" t="str">
         <f>B15&amp;G2&amp;D1</f>
@@ -3667,7 +3674,7 @@
       </c>
       <c r="I15" t="str">
         <f>I3&amp;B15&amp;D2</f>
-        <v>أَنْ تَكْرُمُوْا</v>
+        <v>لَنْ تَكْرُمُوْا</v>
       </c>
       <c r="J15" t="str">
         <f>L2&amp;D1&amp;F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;F1&amp;G2&amp;H1&amp;D1</f>
@@ -3706,7 +3713,7 @@
       </c>
       <c r="D17" t="str">
         <f>C5&amp;D1&amp;C6&amp;D3&amp;C7&amp;G1&amp;F2&amp;E1</f>
-        <v>كَرَمْتِ</v>
+        <v>كَرُمْتِ</v>
       </c>
       <c r="E17" t="str">
         <f>B17&amp;G2&amp;D1</f>
@@ -3726,7 +3733,7 @@
       </c>
       <c r="I17" t="str">
         <f>I3&amp;B17</f>
-        <v>أَنْ تَكْرُمِيْ</v>
+        <v>لَنْ تَكْرُمِيْ</v>
       </c>
       <c r="J17" t="str">
         <f>L2&amp;D1&amp;F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;E1&amp;G2&amp;H1&amp;D1</f>
@@ -3761,7 +3768,7 @@
       </c>
       <c r="D18" s="10" t="str">
         <f>C5&amp;D1&amp;C6&amp;D3&amp;C7&amp;G1&amp;F2&amp;F1&amp;H2&amp;D1&amp;D2</f>
-        <v>كَرَمْتُمَا</v>
+        <v>كَرُمْتُمَا</v>
       </c>
       <c r="E18" s="10" t="str">
         <f>B18&amp;G2&amp;E1</f>
@@ -3781,7 +3788,7 @@
       </c>
       <c r="I18" s="10" t="str">
         <f>I3&amp;B18</f>
-        <v>أَنْ تَكْرُمَا</v>
+        <v>لَنْ تَكْرُمَا</v>
       </c>
       <c r="J18" s="10" t="str">
         <f>L2&amp;D1&amp;F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;D2&amp;G2&amp;H1&amp;E1</f>
@@ -3808,7 +3815,7 @@
       </c>
       <c r="D19" t="str">
         <f>C5&amp;D1&amp;C6&amp;D3&amp;C7&amp;G1&amp;F2&amp;F1&amp;G2&amp;H1&amp;D1</f>
-        <v>كَرَمْتُنَّ</v>
+        <v>كَرُمْتُنَّ</v>
       </c>
       <c r="E19" t="str">
         <f>B19</f>
@@ -3828,7 +3835,7 @@
       </c>
       <c r="I19" t="str">
         <f>I3&amp;B19</f>
-        <v>أَنْ تَكْرُمْنَ</v>
+        <v>لَنْ تَكْرُمْنَ</v>
       </c>
       <c r="J19" t="str">
         <f>L2&amp;D1&amp;F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;G1&amp;G2&amp;D1&amp;D2&amp;G2&amp;H1&amp;E1</f>
@@ -3859,7 +3866,7 @@
       </c>
       <c r="D21" t="str">
         <f>C5&amp;D1&amp;C6&amp;D3&amp;C7&amp;G1&amp;F2&amp;F1</f>
-        <v>كَرَمْتُ</v>
+        <v>كَرُمْتُ</v>
       </c>
       <c r="E21" t="str">
         <f>B21&amp;F1</f>
@@ -3879,7 +3886,7 @@
       </c>
       <c r="I21" t="str">
         <f>I3&amp;B21&amp;D1</f>
-        <v>أَنْ أَكْرُمَ</v>
+        <v>لَنْ أَكْرُمَ</v>
       </c>
       <c r="J21" t="str">
         <f>L2&amp;D1&amp;J2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;G2&amp;H1&amp;D1</f>
@@ -3914,7 +3921,7 @@
       </c>
       <c r="D22" t="str">
         <f>C5&amp;D1&amp;C6&amp;D3&amp;C7&amp;G1&amp;G2&amp;D1&amp;D2</f>
-        <v>كَرَمْنَا</v>
+        <v>كَرُمْنَا</v>
       </c>
       <c r="E22" t="str">
         <f>B22&amp;F1</f>
@@ -3934,7 +3941,7 @@
       </c>
       <c r="I22" t="str">
         <f>I3&amp;B22&amp;D1</f>
-        <v>أَنْ نَكْرُمَ</v>
+        <v>لَنْ نَكْرُمَ</v>
       </c>
       <c r="J22" t="str">
         <f>L2&amp;D1&amp;G2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E3&amp;C7&amp;D1&amp;G2&amp;H1&amp;D1</f>
@@ -3964,7 +3971,7 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D24" s="14" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E24" s="14"/>
       <c r="F24" s="14"/>
@@ -3997,6 +4004,9 @@
         <f>C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;K1</f>
         <v>كَارِمٌ</v>
       </c>
+      <c r="J25" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D26" t="str">
@@ -4015,10 +4025,13 @@
         <f>C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;D1&amp;I2&amp;G1&amp;G2&amp;E1</f>
         <v>كَارِمَيْنِ</v>
       </c>
+      <c r="J26" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D28" s="14" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
@@ -4051,6 +4064,9 @@
         <f>H2&amp;D1&amp;C5&amp;G1&amp;C6&amp;F1&amp;E2&amp;G1&amp;C7&amp;K1</f>
         <v>مَكْرُوْمٌ</v>
       </c>
+      <c r="J29" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D30" t="str">
@@ -4069,10 +4085,13 @@
         <f>H2&amp;D1&amp;C5&amp;G1&amp;C6&amp;F1&amp;E2&amp;G1&amp;C7&amp;D1&amp;I2&amp;G1&amp;G2&amp;E1</f>
         <v>مَكْرُوْمَيْنِ</v>
       </c>
+      <c r="J30" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D32" s="14" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E32" s="14"/>
       <c r="F32" s="14"/>
@@ -4118,7 +4137,7 @@
     </row>
     <row r="36" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D36" s="14" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
@@ -4152,7 +4171,7 @@
     </row>
     <row r="40" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D40" s="14" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E40" s="14"/>
       <c r="F40" s="14"/>
@@ -4189,19 +4208,19 @@
     <row r="43" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D43" s="3"/>
       <c r="E43" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="4:9" x14ac:dyDescent="0.25">
@@ -4237,7 +4256,7 @@
     </row>
     <row r="46" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D46" s="14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
@@ -4275,22 +4294,22 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D49" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G49" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H49" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H49" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="I49" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -4329,7 +4348,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D52" s="14" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E52" s="14"/>
       <c r="F52" s="14"/>
@@ -4365,21 +4384,21 @@
         <v/>
       </c>
       <c r="E55" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F55" s="5" t="str">
         <f>IF(G54, H2&amp;E1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;D1&amp;K2&amp;K1,"")</f>
         <v/>
       </c>
       <c r="G55" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H55" s="5" t="str">
         <f>IF(I54, H2&amp;E1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;K1,"")</f>
         <v/>
       </c>
       <c r="I55" s="4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -4388,21 +4407,21 @@
         <v/>
       </c>
       <c r="E56" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F56" s="5" t="str">
         <f>IF(G54, H2&amp;E1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;D1&amp;F2&amp;D1&amp;D2&amp;G2&amp;E1,"")</f>
         <v/>
       </c>
       <c r="G56" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H56" s="5" t="str">
         <f>IF(I54, H2&amp;E1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;D1&amp;D2&amp;G2&amp;E1,"")</f>
         <v/>
       </c>
       <c r="I56" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -4411,26 +4430,26 @@
         <v/>
       </c>
       <c r="E57" s="6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F57" s="5" t="str">
         <f>IF(G54, H2&amp;D1&amp;C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;F1,"")</f>
         <v/>
       </c>
       <c r="G57" s="6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H57" s="5" t="str">
         <f>IF(I54, H2&amp;D1&amp;C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;F1,"")</f>
         <v/>
       </c>
       <c r="I57" s="6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="14" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E59" s="14"/>
       <c r="F59" s="14"/>
@@ -4503,10 +4522,10 @@
         <v/>
       </c>
       <c r="N61" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="O61" s="7" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q61" t="b">
         <v>0</v>
@@ -4555,10 +4574,10 @@
         <v/>
       </c>
       <c r="N62" s="7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="O62" s="7" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="Q62" t="b">
         <v>0</v>
@@ -4607,10 +4626,10 @@
         <v/>
       </c>
       <c r="N63" s="7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="O63" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Q63" t="b">
         <v>0</v>
@@ -4659,10 +4678,10 @@
         <v/>
       </c>
       <c r="N64" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O64" s="7" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="Q64" t="b">
         <v>0</v>
@@ -4711,10 +4730,10 @@
         <v/>
       </c>
       <c r="N65" s="7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="O65" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="Q65" t="b">
         <v>0</v>
@@ -4768,10 +4787,10 @@
         <v/>
       </c>
       <c r="N67" s="7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="O67" s="7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Q67" t="b">
         <v>0</v>
@@ -4804,10 +4823,10 @@
         <v/>
       </c>
       <c r="N68" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="O68" s="7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="Q68" t="b">
         <v>0</v>
@@ -4840,10 +4859,10 @@
         <v/>
       </c>
       <c r="N69" s="7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="O69" s="7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="Q69" t="b">
         <v>0</v>
@@ -4892,10 +4911,10 @@
         <v/>
       </c>
       <c r="N70" s="7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="O70" s="7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="Q70" t="b">
         <v>0</v>

--- a/Arabic Sarf Template.xlsx
+++ b/Arabic Sarf Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\HGWC\Aalim Course\Books and Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB1A0D1-EF4C-4D02-8E86-A0838AB042B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B045F38E-79E7-45FD-84DB-96E29C4D8D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8190" yWindow="0" windowWidth="15810" windowHeight="12900" xr2:uid="{0CB986DA-EAA0-487E-8422-15F5F0704A7F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{0CB986DA-EAA0-487E-8422-15F5F0704A7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Base - Template" sheetId="1" r:id="rId1"/>
@@ -204,7 +204,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="93">
   <si>
     <t>َ</t>
   </si>
@@ -467,9 +467,6 @@
     <t>Rafa'</t>
   </si>
   <si>
-    <t>Nasab &amp; Jarr</t>
-  </si>
-  <si>
     <t>الفعل الماضي المرفوع</t>
   </si>
   <si>
@@ -480,6 +477,12 @@
   </si>
   <si>
     <t>الفعل المضارع المجهول</t>
+  </si>
+  <si>
+    <t>Nasab</t>
+  </si>
+  <si>
+    <t>Jarr</t>
   </si>
 </sst>
 </file>
@@ -603,7 +606,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$Q$61" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$Q$61" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
@@ -647,7 +650,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$Q$62" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$Q$62" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
@@ -667,31 +670,31 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$Q$63" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$Q$63" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$Q$64" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$Q$64" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$Q$65" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$Q$65" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$Q$67" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$Q$67" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$Q$68" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$Q$68" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$Q$69" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$Q$69" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$Q$70" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$Q$70" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3122,16 +3125,16 @@
     </row>
     <row r="4" spans="1:21" s="1" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="D4" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="F4" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="12" t="s">
         <v>90</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>91</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>24</v>
@@ -4017,6 +4020,10 @@
         <f>C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;D1&amp;F2&amp;D1&amp;I2&amp;G1&amp;G2&amp;E1</f>
         <v>كَارِمَتَيْنِ</v>
       </c>
+      <c r="F26" t="str">
+        <f>C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;D1&amp;K2&amp;I1</f>
+        <v>كَارِمَةً</v>
+      </c>
       <c r="G26" t="str">
         <f>C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;E1&amp;I2&amp;G1&amp;G2&amp;D1</f>
         <v>كَارِمِيْنَ</v>
@@ -4025,8 +4032,41 @@
         <f>C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;D1&amp;I2&amp;G1&amp;G2&amp;E1</f>
         <v>كَارِمَيْنِ</v>
       </c>
+      <c r="I26" t="str">
+        <f>C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;I1</f>
+        <v>كَارِمً</v>
+      </c>
       <c r="J26" t="s">
-        <v>87</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D27" t="str">
+        <f>C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;D1&amp;D2&amp;F2&amp;J1</f>
+        <v>كَارِمَاتٍ</v>
+      </c>
+      <c r="E27" t="str">
+        <f>C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;D1&amp;F2&amp;D1&amp;I2&amp;G1&amp;G2&amp;E1</f>
+        <v>كَارِمَتَيْنِ</v>
+      </c>
+      <c r="F27" t="str">
+        <f>C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;D1&amp;K2&amp;J1</f>
+        <v>كَارِمَةٍ</v>
+      </c>
+      <c r="G27" t="str">
+        <f>C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;E1&amp;I2&amp;G1&amp;G2&amp;D1</f>
+        <v>كَارِمِيْنَ</v>
+      </c>
+      <c r="H27" t="str">
+        <f>C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;D1&amp;I2&amp;G1&amp;G2&amp;E1</f>
+        <v>كَارِمَيْنِ</v>
+      </c>
+      <c r="I27" t="str">
+        <f>C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;J1</f>
+        <v>كَارِمٍ</v>
+      </c>
+      <c r="J27" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -4077,6 +4117,10 @@
         <f>H2&amp;D1&amp;C5&amp;G1&amp;C6&amp;F1&amp;E2&amp;G1&amp;C7&amp;D1&amp;F2&amp;D1&amp;I2&amp;G1&amp;G2&amp;E1</f>
         <v>مَكْرُوْمَتَيْنِ</v>
       </c>
+      <c r="F30" t="str">
+        <f>H2&amp;D1&amp;C5&amp;G1&amp;C6&amp;F1&amp;E2&amp;G1&amp;C7&amp;D1&amp;K2&amp;I1</f>
+        <v>مَكْرُوْمَةً</v>
+      </c>
       <c r="G30" t="str">
         <f>H2&amp;D1&amp;C5&amp;G1&amp;C6&amp;F1&amp;E2&amp;G1&amp;C7&amp;E1&amp;I2&amp;G1&amp;G2&amp;D1</f>
         <v>مَكْرُوْمِيْنَ</v>
@@ -4085,8 +4129,41 @@
         <f>H2&amp;D1&amp;C5&amp;G1&amp;C6&amp;F1&amp;E2&amp;G1&amp;C7&amp;D1&amp;I2&amp;G1&amp;G2&amp;E1</f>
         <v>مَكْرُوْمَيْنِ</v>
       </c>
+      <c r="I30" t="str">
+        <f>H2&amp;D1&amp;C5&amp;G1&amp;C6&amp;F1&amp;E2&amp;G1&amp;C7&amp;I1</f>
+        <v>مَكْرُوْمً</v>
+      </c>
       <c r="J30" t="s">
-        <v>87</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D31" t="str">
+        <f>H2&amp;D1&amp;C5&amp;G1&amp;C6&amp;F1&amp;E2&amp;G1&amp;C7&amp;D1&amp;D2&amp;F2&amp;J1</f>
+        <v>مَكْرُوْمَاتٍ</v>
+      </c>
+      <c r="E31" t="str">
+        <f>H2&amp;D1&amp;C5&amp;G1&amp;C6&amp;F1&amp;E2&amp;G1&amp;C7&amp;D1&amp;F2&amp;D1&amp;I2&amp;G1&amp;G2&amp;E1</f>
+        <v>مَكْرُوْمَتَيْنِ</v>
+      </c>
+      <c r="F31" t="str">
+        <f>H2&amp;D1&amp;C5&amp;G1&amp;C6&amp;F1&amp;E2&amp;G1&amp;C7&amp;D1&amp;K2&amp;J1</f>
+        <v>مَكْرُوْمَةٍ</v>
+      </c>
+      <c r="G31" t="str">
+        <f>H2&amp;D1&amp;C5&amp;G1&amp;C6&amp;F1&amp;E2&amp;G1&amp;C7&amp;D1&amp;I2&amp;G1&amp;G2&amp;E1</f>
+        <v>مَكْرُوْمَيْنِ</v>
+      </c>
+      <c r="H31" t="str">
+        <f>H2&amp;D1&amp;C5&amp;G1&amp;C6&amp;F1&amp;E2&amp;G1&amp;C7&amp;D1&amp;I2&amp;G1&amp;G2&amp;E1</f>
+        <v>مَكْرُوْمَيْنِ</v>
+      </c>
+      <c r="I31" t="str">
+        <f>H2&amp;D1&amp;C5&amp;G1&amp;C6&amp;F1&amp;E2&amp;G1&amp;C7&amp;J1</f>
+        <v>مَكْرُوْمٍ</v>
+      </c>
+      <c r="J31" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -4483,43 +4560,43 @@
       <c r="C61" s="7"/>
       <c r="D61" t="str">
         <f>IF(Q61, L2&amp;D1&amp;D2&amp;F2&amp;F1&amp;C5&amp;G1&amp;C6&amp;E1&amp;C7&amp;G1, "")</f>
-        <v/>
+        <v>لَاتُكْرِمْ</v>
       </c>
       <c r="E61" t="str">
         <f>IF(Q61, J2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E1&amp;C7&amp;G1, "")</f>
-        <v/>
+        <v>أَكْرِمْ</v>
       </c>
       <c r="F61" t="str">
         <f>IF(Q61, H2&amp;F1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;K1, "")</f>
-        <v/>
+        <v>مُكْرَمٌ</v>
       </c>
       <c r="G61" t="str">
         <f>IF(Q61, D2&amp;E1&amp;C5&amp;G1&amp;C6&amp;D1&amp;D2&amp;C7&amp;I1&amp;D2, "")</f>
-        <v/>
+        <v>اِكْرَامًا</v>
       </c>
       <c r="H61" t="str">
         <f>IF(Q61, I2&amp;F1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;F1, "")</f>
-        <v/>
+        <v>يُكْرَمُ</v>
       </c>
       <c r="I61" t="str">
         <f>IF(Q61, J2&amp;F1&amp;C5&amp;G1&amp;C6&amp;E1&amp;C7&amp;D1, "")</f>
-        <v/>
+        <v>أُكْرِمَ</v>
       </c>
       <c r="J61" t="str">
         <f>IF(Q61, H2&amp;F1&amp;C5&amp;G1&amp;C6&amp;E1&amp;C7&amp;K1, "")</f>
-        <v/>
+        <v>مُكْرِمٌ</v>
       </c>
       <c r="K61" t="str">
         <f>IF(Q61, D2&amp;E1&amp;C5&amp;G1&amp;C6&amp;D1&amp;D2&amp;C7&amp;I1&amp;D2, "")</f>
-        <v/>
+        <v>اِكْرَامًا</v>
       </c>
       <c r="L61" t="str">
         <f>IF(Q61, I2&amp;F1&amp;C5&amp;G1&amp;C6&amp;E1&amp;C7&amp;F1, "")</f>
-        <v/>
+        <v>يُكْرِمُ</v>
       </c>
       <c r="M61" t="str">
         <f>IF(Q61, J2&amp;D1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;D1, "")</f>
-        <v/>
+        <v>أَكْرَمَ</v>
       </c>
       <c r="N61" s="7" t="s">
         <v>64</v>
@@ -4528,50 +4605,50 @@
         <v>65</v>
       </c>
       <c r="Q61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C62" s="7"/>
       <c r="D62" t="str">
         <f>IF(Q62, L2&amp;D1&amp;D2&amp;F2&amp;F1&amp;C5&amp;D1&amp;C6&amp;H1&amp;E1&amp;C7&amp;G1, "")</f>
-        <v/>
+        <v>لَاتُكَرِّمْ</v>
       </c>
       <c r="E62" t="str">
         <f>IF(Q62, C5&amp;D1&amp;C6&amp;H1&amp;E1&amp;C7&amp;G1, "")</f>
-        <v/>
+        <v>كَرِّمْ</v>
       </c>
       <c r="F62" t="str">
         <f>IF(Q62, H2&amp;F1&amp;C5&amp;D1&amp;C6&amp;H1&amp;D1&amp;C7&amp;K1, "")</f>
-        <v/>
+        <v>مُكَرَّمٌ</v>
       </c>
       <c r="G62" t="str">
         <f>IF(Q62, F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E1&amp;I2&amp;G1&amp;C7&amp;I1&amp;D2, "")</f>
-        <v/>
+        <v>تَكْرِيْمًا</v>
       </c>
       <c r="H62" t="str">
         <f>IF(Q62, I2&amp;F1&amp;C5&amp;D1&amp;C6&amp;H1&amp;D1&amp;C7&amp;F1, "")</f>
-        <v/>
+        <v>يُكَرَّمُ</v>
       </c>
       <c r="I62" t="str">
         <f>IF(Q62, C5&amp;F1&amp;C6&amp;H1&amp;E1&amp;C7&amp;D1, "")</f>
-        <v/>
+        <v>كُرِّمَ</v>
       </c>
       <c r="J62" t="str">
         <f>IF(Q62, H2&amp;F1&amp;C5&amp;D1&amp;C6&amp;H1&amp;E1&amp;C7&amp;K1, "")</f>
-        <v/>
+        <v>مُكَرِّمٌ</v>
       </c>
       <c r="K62" t="str">
         <f>IF(Q62, F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E1&amp;I2&amp;G1&amp;C7&amp;I1&amp;D2, "")</f>
-        <v/>
+        <v>تَكْرِيْمًا</v>
       </c>
       <c r="L62" t="str">
         <f>IF(Q62, I2&amp;F1&amp;C5&amp;D1&amp;C6&amp;H1&amp;E1&amp;C7&amp;F1, "")</f>
-        <v/>
+        <v>يُكَرِّمُ</v>
       </c>
       <c r="M62" t="str">
         <f>IF(Q62, C5&amp;D1&amp;C6&amp;H1&amp;D1&amp;C7&amp;D1, "")</f>
-        <v/>
+        <v>كَرَّمَ</v>
       </c>
       <c r="N62" s="7" t="s">
         <v>66</v>
@@ -4580,50 +4657,50 @@
         <v>67</v>
       </c>
       <c r="Q62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C63" s="7"/>
       <c r="D63" t="str">
         <f>IF(Q63, L2&amp;D1&amp;D2&amp;F2&amp;F1&amp;C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;G1, "")</f>
-        <v/>
+        <v>لَاتُكَارِمْ</v>
       </c>
       <c r="E63" t="str">
         <f>IF(Q63, C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;G1, "")</f>
-        <v/>
+        <v>كَارِمْ</v>
       </c>
       <c r="F63" t="str">
         <f>IF(Q63, H2&amp;F1&amp;C5&amp;D1&amp;D2&amp;C6&amp;D1&amp;C7&amp;K1, "")</f>
-        <v/>
+        <v>مُكَارَمٌ</v>
       </c>
       <c r="G63" t="str">
         <f>IF(Q63, H2&amp;F1&amp;C5&amp;D1&amp;D2&amp;C6&amp;D1&amp;C7&amp;D1&amp;K2&amp;I1, "")</f>
-        <v/>
+        <v>مُكَارَمَةً</v>
       </c>
       <c r="H63" t="str">
         <f>IF(Q63, I2&amp;F1&amp;C5&amp;D1&amp;D2&amp;C6&amp;D1&amp;C7&amp;F1, "")</f>
-        <v/>
+        <v>يُكَارَمُ</v>
       </c>
       <c r="I63" t="str">
         <f>IF(Q63, C5&amp;F1&amp;E2&amp;G1&amp;C6&amp;E1&amp;C7&amp;D1, "")</f>
-        <v/>
+        <v>كُوْرِمَ</v>
       </c>
       <c r="J63" t="str">
         <f>IF(Q63, H2&amp;F1&amp;C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;K1, "")</f>
-        <v/>
+        <v>مُكَارِمٌ</v>
       </c>
       <c r="K63" t="str">
         <f>IF(Q63, H2&amp;F1&amp;C5&amp;D1&amp;D2&amp;C6&amp;D1&amp;C7&amp;D1&amp;K2&amp;I1&amp;L1&amp;C5&amp;E1&amp;C6&amp;D1&amp;D2&amp;C7&amp;I1&amp;D2, "")</f>
-        <v/>
+        <v>مُكَارَمَةً / كِرَامًا</v>
       </c>
       <c r="L63" t="str">
         <f>IF(Q63, I2&amp;F1&amp;C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;F1, "")</f>
-        <v/>
+        <v>يُكَارِمُ</v>
       </c>
       <c r="M63" t="str">
         <f>IF(Q63, C5&amp;D1&amp;D2&amp;C6&amp;D1&amp;C7&amp;D1, "")</f>
-        <v/>
+        <v>كَارَمَ</v>
       </c>
       <c r="N63" s="7" t="s">
         <v>68</v>
@@ -4632,50 +4709,50 @@
         <v>69</v>
       </c>
       <c r="Q63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C64" s="7"/>
       <c r="D64" t="str">
         <f>IF(Q64, L2&amp;D1&amp;D2&amp;F2&amp;D1&amp;F2&amp;D1&amp;C5&amp;D1&amp;C6&amp;H1&amp;D1&amp;C7&amp;G1, "")</f>
-        <v/>
+        <v>لَاتَتَكَرَّمْ</v>
       </c>
       <c r="E64" t="str">
         <f>IF(Q64, F2&amp;D1&amp;C5&amp;D1&amp;C6&amp;H1&amp;D1&amp;C7&amp;G1, "")</f>
-        <v/>
+        <v>تَكَرَّمْ</v>
       </c>
       <c r="F64" t="str">
         <f>IF(Q64, H2&amp;F1&amp;F2&amp;D1&amp;C5&amp;D1&amp;C6&amp;H1&amp;D1&amp;C7&amp;K1, "")</f>
-        <v/>
+        <v>مُتَكَرَّمٌ</v>
       </c>
       <c r="G64" t="str">
         <f>IF(Q64, F2&amp;D1&amp;C5&amp;D1&amp;C6&amp;H1&amp;F1&amp;C7&amp;I1&amp;D2, "")</f>
-        <v/>
+        <v>تَكَرُّمًا</v>
       </c>
       <c r="H64" t="str">
         <f>IF(Q64, I2&amp;F1&amp;F2&amp;D1&amp;C5&amp;D1&amp;C6&amp;H1&amp;D1&amp;C7&amp;F1, "")</f>
-        <v/>
+        <v>يُتَكَرَّمُ</v>
       </c>
       <c r="I64" t="str">
         <f>IF(Q64, F2&amp;F1&amp;C5&amp;F1&amp;C6&amp;H1&amp;E1&amp;C7&amp;D1, "")</f>
-        <v/>
+        <v>تُكُرِّمَ</v>
       </c>
       <c r="J64" t="str">
         <f>IF(Q64, H2&amp;F1&amp;F2&amp;D1&amp;C5&amp;D1&amp;C6&amp;H1&amp;E1&amp;C7&amp;K1, "")</f>
-        <v/>
+        <v>مُتَكَرِّمٌ</v>
       </c>
       <c r="K64" t="str">
         <f>IF(Q64, F2&amp;D1&amp;C5&amp;D1&amp;C6&amp;H1&amp;F1&amp;C7&amp;I1&amp;D2, "")</f>
-        <v/>
+        <v>تَكَرُّمًا</v>
       </c>
       <c r="L64" t="str">
         <f>IF(Q64, I2&amp;D1&amp;F2&amp;D1&amp;C5&amp;D1&amp;C6&amp;H1&amp;D1&amp;C7&amp;F1, "")</f>
-        <v/>
+        <v>يَتَكَرَّمُ</v>
       </c>
       <c r="M64" t="str">
         <f>IF(Q64, F2&amp;D1&amp;C5&amp;D1&amp;C6&amp;H1&amp;D1&amp;C7&amp;D1, "")</f>
-        <v/>
+        <v>تَكَرَّمَ</v>
       </c>
       <c r="N64" s="7" t="s">
         <v>70</v>
@@ -4684,50 +4761,50 @@
         <v>71</v>
       </c>
       <c r="Q64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C65" s="7"/>
       <c r="D65" t="str">
         <f>IF(Q65, L2&amp;D1&amp;D2&amp;F2&amp;D1&amp;F2&amp;D1&amp;C5&amp;D1&amp;D2&amp;C6&amp;D1&amp;C7&amp;G1, "")</f>
-        <v/>
+        <v>لَاتَتَكَارَمْ</v>
       </c>
       <c r="E65" t="str">
         <f>IF(Q65, F2&amp;D1&amp;C5&amp;D1&amp;D2&amp;C6&amp;D1&amp;C7&amp;G1, "")</f>
-        <v/>
+        <v>تَكَارَمْ</v>
       </c>
       <c r="F65" t="str">
         <f>IF(Q65, H2&amp;F1&amp;F2&amp;D1&amp;C5&amp;D1&amp;D2&amp;C6&amp;D1&amp;C7&amp;K1, "")</f>
-        <v/>
+        <v>مُتَكَارَمٌ</v>
       </c>
       <c r="G65" t="str">
         <f>IF(Q65, F2&amp;D1&amp;C5&amp;D1&amp;D2&amp;C6&amp;F1&amp;C7&amp;I1&amp;D2, "")</f>
-        <v/>
+        <v>تَكَارُمًا</v>
       </c>
       <c r="H65" t="str">
         <f>IF(Q65, I2&amp;F1&amp;F2&amp;D1&amp;C5&amp;D1&amp;D2&amp;C6&amp;D1&amp;C7&amp;F1, "")</f>
-        <v/>
+        <v>يُتَكَارَمُ</v>
       </c>
       <c r="I65" t="str">
         <f>IF(Q65, F2&amp;F1&amp;C5&amp;F1&amp;E2&amp;G1&amp;C6&amp;E1&amp;C7&amp;D1, "")</f>
-        <v/>
+        <v>تُكُوْرِمَ</v>
       </c>
       <c r="J65" t="str">
         <f>IF(Q65, H2&amp;F1&amp;F2&amp;D1&amp;C5&amp;D1&amp;D2&amp;C6&amp;E1&amp;C7&amp;K1, "")</f>
-        <v/>
+        <v>مُتَكَارِمٌ</v>
       </c>
       <c r="K65" t="str">
         <f>IF(Q65, F2&amp;D1&amp;C5&amp;D1&amp;D2&amp;C6&amp;F1&amp;C7&amp;I1&amp;D2, "")</f>
-        <v/>
+        <v>تَكَارُمًا</v>
       </c>
       <c r="L65" t="str">
         <f>IF(Q65, I2&amp;D1&amp;F2&amp;D1&amp;C5&amp;D1&amp;D2&amp;C6&amp;D1&amp;C7&amp;F1, "")</f>
-        <v/>
+        <v>يَتَكَارَمُ</v>
       </c>
       <c r="M65" t="str">
         <f>IF(Q65, F2&amp;D1&amp;C5&amp;D1&amp;D2&amp;C6&amp;D1&amp;C7&amp;D1, "")</f>
-        <v/>
+        <v>تَكَارَمَ</v>
       </c>
       <c r="N65" s="7" t="s">
         <v>72</v>
@@ -4736,7 +4813,7 @@
         <v>73</v>
       </c>
       <c r="Q65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="3:17" x14ac:dyDescent="0.25">
@@ -4748,43 +4825,43 @@
       <c r="C67" s="7"/>
       <c r="D67" t="str">
         <f>IF(Q67, L2&amp;D1&amp;D2&amp;F2&amp;D1&amp;C5&amp;G1&amp;F2&amp;D1&amp;C6&amp;E1&amp;C7&amp;G1, "")</f>
-        <v/>
+        <v>لَاتَكْتَرِمْ</v>
       </c>
       <c r="E67" t="str">
         <f>IF(Q67, D2&amp;E1&amp;C5&amp;G1&amp;F2&amp;D1&amp;C6&amp;E1&amp;C7&amp;G1, "")</f>
-        <v/>
+        <v>اِكْتَرِمْ</v>
       </c>
       <c r="F67" t="str">
         <f>IF(Q67, H2&amp;F1&amp;C5&amp;G1&amp;F2&amp;D1&amp;C6&amp;D1&amp;C7&amp;K1, "")</f>
-        <v/>
+        <v>مُكْتَرَمٌ</v>
       </c>
       <c r="G67" t="str">
         <f>IF(Q67, D2&amp;E1&amp;C5&amp;G1&amp;F2&amp;E1&amp;C6&amp;D1&amp;D2&amp;C7&amp;I1&amp;D2, "")</f>
-        <v/>
+        <v>اِكْتِرَامًا</v>
       </c>
       <c r="H67" t="str">
         <f>IF(Q67, I2&amp;F1&amp;C5&amp;G1&amp;F2&amp;D1&amp;C6&amp;D1&amp;C7&amp;F1, "")</f>
-        <v/>
+        <v>يُكْتَرَمُ</v>
       </c>
       <c r="I67" t="str">
         <f>IF(Q67, D2&amp;F1&amp;C5&amp;G1&amp;F2&amp;F1&amp;C6&amp;E1&amp;C7&amp;D1, "")</f>
-        <v/>
+        <v>اُكْتُرِمَ</v>
       </c>
       <c r="J67" t="str">
         <f>IF(Q67, H2&amp;F1&amp;C5&amp;G1&amp;F2&amp;D1&amp;C6&amp;E1&amp;C7&amp;K1, "")</f>
-        <v/>
+        <v>مُكْتَرِمٌ</v>
       </c>
       <c r="K67" t="str">
         <f>IF(Q67, D2&amp;E1&amp;C5&amp;G1&amp;F2&amp;E1&amp;C6&amp;D1&amp;D2&amp;C7&amp;I1&amp;D2, "")</f>
-        <v/>
+        <v>اِكْتِرَامًا</v>
       </c>
       <c r="L67" t="str">
         <f>IF(Q67, I2&amp;D1&amp;C5&amp;G1&amp;F2&amp;D1&amp;C6&amp;E1&amp;C7&amp;F1, "")</f>
-        <v/>
+        <v>يَكْتَرِمُ</v>
       </c>
       <c r="M67" t="str">
         <f>IF(Q67, D2&amp;E1&amp;C5&amp;G1&amp;F2&amp;D1&amp;C6&amp;D1&amp;C7&amp;D1, "")</f>
-        <v/>
+        <v>اِكْتَرَمَ</v>
       </c>
       <c r="N67" s="7" t="s">
         <v>74</v>
@@ -4793,34 +4870,34 @@
         <v>75</v>
       </c>
       <c r="Q67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C68" s="7"/>
       <c r="D68" t="str">
         <f>IF(Q68, L2&amp;D1&amp;D2&amp;F2&amp;D1&amp;G2&amp;G1&amp;C5&amp;D1&amp;C6&amp;E1&amp;C7&amp;G1, "")</f>
-        <v/>
+        <v>لَاتَنْكَرِمْ</v>
       </c>
       <c r="E68" t="str">
         <f>IF(Q68, D2&amp;E1&amp;G2&amp;G1&amp;C5&amp;D1&amp;C6&amp;E1&amp;C7&amp;G1, "")</f>
-        <v/>
+        <v>اِنْكَرِمْ</v>
       </c>
       <c r="J68" t="str">
         <f>IF(Q68, H2&amp;F1&amp;G2&amp;G1&amp;C5&amp;D1&amp;C6&amp;E1&amp;C7&amp;K1, "")</f>
-        <v/>
+        <v>مُنْكَرِمٌ</v>
       </c>
       <c r="K68" t="str">
         <f>IF(Q68, D2&amp;E1&amp;G2&amp;G1&amp;C5&amp;E1&amp;C6&amp;D1&amp;D2&amp;C7&amp;I1&amp;D2, "")</f>
-        <v/>
+        <v>اِنْكِرَامًا</v>
       </c>
       <c r="L68" t="str">
         <f>IF(Q68, I2&amp;D1&amp;G2&amp;G1&amp;C5&amp;D1&amp;C6&amp;E1&amp;C7&amp;F1, "")</f>
-        <v/>
+        <v>يَنْكَرِمُ</v>
       </c>
       <c r="M68" t="str">
         <f>IF(Q68, D2&amp;E1&amp;G2&amp;G1&amp;C5&amp;D1&amp;C6&amp;D1&amp;C7&amp;D1, "")</f>
-        <v/>
+        <v>اِنْكَرَمَ</v>
       </c>
       <c r="N68" s="7" t="s">
         <v>76</v>
@@ -4829,34 +4906,34 @@
         <v>77</v>
       </c>
       <c r="Q68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C69" s="7"/>
       <c r="D69" t="str">
         <f>IF(Q69, L2&amp;D1&amp;D2&amp;F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;H1&amp;D1, "")</f>
-        <v/>
+        <v>لَاتَكْرَمَّ</v>
       </c>
       <c r="E69" t="str">
         <f>IF(Q69, D2&amp;E1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;H1&amp;D1, "")</f>
-        <v/>
+        <v>اِكْرَمَّ</v>
       </c>
       <c r="J69" t="str">
         <f>IF(Q69, H2&amp;F1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;H1&amp;K1, "")</f>
-        <v/>
+        <v>مُكْرَمٌّ</v>
       </c>
       <c r="K69" t="str">
         <f>IF(Q69, D2&amp;E1&amp;C5&amp;G1&amp;C6&amp;E1&amp;C7&amp;D1&amp;D2&amp;C7&amp;I1&amp;D2, "")</f>
-        <v/>
+        <v>اِكْرِمَامًا</v>
       </c>
       <c r="L69" t="str">
         <f>IF(Q69, I2&amp;D1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;H1&amp;F1, "")</f>
-        <v/>
+        <v>يَكْرَمُّ</v>
       </c>
       <c r="M69" t="str">
         <f>IF(Q69, D2&amp;E1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;H1&amp;D1, "")</f>
-        <v/>
+        <v>اِكْرَمَّ</v>
       </c>
       <c r="N69" s="7" t="s">
         <v>78</v>
@@ -4865,50 +4942,50 @@
         <v>79</v>
       </c>
       <c r="Q69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C70" s="7"/>
       <c r="D70" t="str">
         <f>IF(Q70, L2&amp;D1&amp;D2&amp;F2&amp;D1&amp;N2&amp;G1&amp;F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E1&amp;C7&amp;G1, "")</f>
-        <v/>
+        <v>لَاتَسْتَكْرِمْ</v>
       </c>
       <c r="E70" t="str">
         <f>IF(Q70, D2&amp;E1&amp;N2&amp;G1&amp;F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E1&amp;C7&amp;G1, "")</f>
-        <v/>
+        <v>اِسْتَكْرِمْ</v>
       </c>
       <c r="F70" t="str">
         <f>IF(Q70, H2&amp;F1&amp;N2&amp;G1&amp;F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;K1, "")</f>
-        <v/>
+        <v>مُسْتَكْرَمٌ</v>
       </c>
       <c r="G70" t="str">
         <f>IF(Q70, D2&amp;E1&amp;N2&amp;G1&amp;F2&amp;E1&amp;C5&amp;G1&amp;C6&amp;D1&amp;D2&amp;C7&amp;I1&amp;D2, "")</f>
-        <v/>
+        <v>اِسْتِكْرَامًا</v>
       </c>
       <c r="H70" t="str">
         <f>IF(Q70, I2&amp;F1&amp;N2&amp;G1&amp;F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;F1, "")</f>
-        <v/>
+        <v>يُسْتَكْرَمُ</v>
       </c>
       <c r="I70" t="str">
         <f>IF(Q70, D2&amp;F1&amp;N2&amp;G1&amp;F2&amp;F1&amp;C5&amp;G1&amp;C6&amp;E1&amp;C7&amp;D1, "")</f>
-        <v/>
+        <v>اُسْتُكْرِمَ</v>
       </c>
       <c r="J70" t="str">
         <f>IF(Q70, H2&amp;F1&amp;N2&amp;G1&amp;F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E1&amp;C7&amp;K1, "")</f>
-        <v/>
+        <v>مُسْتَكْرِمٌ</v>
       </c>
       <c r="K70" t="str">
         <f>IF(Q70, D2&amp;E1&amp;N2&amp;G1&amp;F2&amp;E1&amp;C5&amp;G1&amp;C6&amp;D1&amp;D2&amp;C7&amp;I1&amp;D2, "")</f>
-        <v/>
+        <v>اِسْتِكْرَامًا</v>
       </c>
       <c r="L70" t="str">
         <f>IF(Q70, I2&amp;D1&amp;N2&amp;G1&amp;F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;E1&amp;C7&amp;F1, "")</f>
-        <v/>
+        <v>يَسْتَكْرِمُ</v>
       </c>
       <c r="M70" t="str">
         <f>IF(Q70, D2&amp;E1&amp;N2&amp;G1&amp;F2&amp;D1&amp;C5&amp;G1&amp;C6&amp;D1&amp;C7&amp;D1, "")</f>
-        <v/>
+        <v>اِسْتَكْرَمَ</v>
       </c>
       <c r="N70" s="7" t="s">
         <v>80</v>
@@ -4917,7 +4994,7 @@
         <v>81</v>
       </c>
       <c r="Q70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="3:17" x14ac:dyDescent="0.25">
